--- a/experiment/HAT_2CH_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/HAT_2CH_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.76</v>
+        <v>33.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8943</v>
+        <v>0.8942</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.83</v>
+        <v>34.88</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9412</v>
+        <v>0.9418</v>
       </c>
     </row>
     <row r="4">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.78</v>
+        <v>28.79</v>
       </c>
       <c r="C4" t="n">
         <v>0.9201</v>
@@ -494,7 +494,7 @@
         <v>32.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7987</v>
+        <v>0.7985</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.72</v>
+        <v>30.77</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9145</v>
+        <v>0.9147999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.21</v>
+        <v>32.24</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8937</v>
+        <v>0.8939</v>
       </c>
     </row>
   </sheetData>
